--- a/artfynd/Norrbytorps naturreservat artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat artfynd.xlsx
@@ -7559,7 +7559,7 @@
         <v>136329952</v>
       </c>
       <c r="B61" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136330044</v>
       </c>
       <c r="B62" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>136329900</v>
       </c>
       <c r="B88" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>135545619</v>
       </c>
       <c r="B101" t="n">
-        <v>91558</v>
+        <v>91559</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>136422293</v>
       </c>
       <c r="B105" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>136346893</v>
       </c>
       <c r="B153" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>136258592</v>
       </c>
       <c r="B155" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>136330155</v>
       </c>
       <c r="B167" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>136330904</v>
       </c>
       <c r="B168" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>136422137</v>
       </c>
       <c r="B171" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>136258570</v>
       </c>
       <c r="B178" t="n">
-        <v>92765</v>
+        <v>92766</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>136422316</v>
       </c>
       <c r="B179" t="n">
-        <v>92765</v>
+        <v>92766</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>136347172</v>
       </c>
       <c r="B213" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>136261399</v>
       </c>
       <c r="B266" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>136346755</v>
       </c>
       <c r="B284" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>136346850</v>
       </c>
       <c r="B285" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>136394246</v>
       </c>
       <c r="B286" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>136261113</v>
       </c>
       <c r="B335" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>136422457</v>
       </c>
       <c r="B371" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>135827249</v>
       </c>
       <c r="B374" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>136394245</v>
       </c>
       <c r="B376" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>136159865</v>
       </c>
       <c r="B384" t="n">
-        <v>96758</v>
+        <v>96759</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>136423160</v>
       </c>
       <c r="B386" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>136423202</v>
       </c>
       <c r="B389" t="n">
-        <v>92920</v>
+        <v>92921</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         <v>135359246</v>
       </c>
       <c r="B464" t="n">
-        <v>91558</v>
+        <v>91559</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>136139193</v>
       </c>
       <c r="B475" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>136159751</v>
       </c>
       <c r="B476" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -54556,7 +54556,7 @@
         <v>136159959</v>
       </c>
       <c r="B477" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>136159979</v>
       </c>
       <c r="B478" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -54768,7 +54768,7 @@
         <v>136193282</v>
       </c>
       <c r="B479" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -54874,7 +54874,7 @@
         <v>136193424</v>
       </c>
       <c r="B480" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>136232449</v>
       </c>
       <c r="B481" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>136394238</v>
       </c>
       <c r="B482" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -55632,7 +55632,7 @@
         <v>136394243</v>
       </c>
       <c r="B487" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -58340,7 +58340,7 @@
         <v>136394241</v>
       </c>
       <c r="B511" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -58452,7 +58452,7 @@
         <v>136394242</v>
       </c>
       <c r="B512" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         <v>136138429</v>
       </c>
       <c r="B531" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -60615,7 +60615,7 @@
         <v>136422471</v>
       </c>
       <c r="B532" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>136422534</v>
       </c>
       <c r="B533" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>136422649</v>
       </c>
       <c r="B534" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -63356,7 +63356,7 @@
         <v>136234180</v>
       </c>
       <c r="B557" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -63458,7 +63458,7 @@
         <v>136394244</v>
       </c>
       <c r="B558" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -63570,7 +63570,7 @@
         <v>136234148</v>
       </c>
       <c r="B559" t="n">
-        <v>98192</v>
+        <v>98193</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -65435,7 +65435,7 @@
         <v>135827336</v>
       </c>
       <c r="B576" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -65541,7 +65541,7 @@
         <v>136422957</v>
       </c>
       <c r="B577" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -66973,7 +66973,7 @@
         <v>136423088</v>
       </c>
       <c r="B590" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -71726,7 +71726,7 @@
         <v>136268106</v>
       </c>
       <c r="B633" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -73542,7 +73542,7 @@
         <v>136394236</v>
       </c>
       <c r="B649" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -79196,7 +79196,7 @@
         <v>136422855</v>
       </c>
       <c r="B701" t="n">
-        <v>90823</v>
+        <v>90824</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -79522,7 +79522,7 @@
         <v>136422890</v>
       </c>
       <c r="B704" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -80198,7 +80198,7 @@
         <v>136226883</v>
       </c>
       <c r="B710" t="n">
-        <v>96662</v>
+        <v>96663</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -80632,7 +80632,7 @@
         <v>136193016</v>
       </c>
       <c r="B714" t="n">
-        <v>91573</v>
+        <v>91574</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -83158,7 +83158,7 @@
         <v>135358856</v>
       </c>
       <c r="B737" t="n">
-        <v>91558</v>
+        <v>91559</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -83268,7 +83268,7 @@
         <v>136241603</v>
       </c>
       <c r="B738" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -83385,7 +83385,7 @@
         <v>136231090</v>
       </c>
       <c r="B739" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -83487,7 +83487,7 @@
         <v>136138371</v>
       </c>
       <c r="B740" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -83593,7 +83593,7 @@
         <v>136259499</v>
       </c>
       <c r="B741" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -83823,7 +83823,7 @@
         <v>136394237</v>
       </c>
       <c r="B743" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat artfynd.xlsx
@@ -7559,7 +7559,7 @@
         <v>136329952</v>
       </c>
       <c r="B61" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136330044</v>
       </c>
       <c r="B62" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>136330004</v>
       </c>
       <c r="B80" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>136422006</v>
       </c>
       <c r="B81" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>136346607</v>
       </c>
       <c r="B82" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>136346721</v>
       </c>
       <c r="B83" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>136422024</v>
       </c>
       <c r="B84" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>136329900</v>
       </c>
       <c r="B88" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>135545619</v>
       </c>
       <c r="B101" t="n">
-        <v>91559</v>
+        <v>91572</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>136422293</v>
       </c>
       <c r="B105" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>136258642</v>
       </c>
       <c r="B111" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>136346893</v>
       </c>
       <c r="B153" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>136258592</v>
       </c>
       <c r="B155" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>136330155</v>
       </c>
       <c r="B167" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>136330904</v>
       </c>
       <c r="B168" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>136422137</v>
       </c>
       <c r="B171" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>136258570</v>
       </c>
       <c r="B178" t="n">
-        <v>92766</v>
+        <v>92779</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>136422316</v>
       </c>
       <c r="B179" t="n">
-        <v>92766</v>
+        <v>92779</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>136347172</v>
       </c>
       <c r="B213" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>136261399</v>
       </c>
       <c r="B266" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>136346755</v>
       </c>
       <c r="B284" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>136346850</v>
       </c>
       <c r="B285" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>136394246</v>
       </c>
       <c r="B286" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>136346730</v>
       </c>
       <c r="B306" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>136261113</v>
       </c>
       <c r="B335" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>136260416</v>
       </c>
       <c r="B344" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>135827212</v>
       </c>
       <c r="B350" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>136422417</v>
       </c>
       <c r="B351" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>136422435</v>
       </c>
       <c r="B352" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>136346869</v>
       </c>
       <c r="B353" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>136422457</v>
       </c>
       <c r="B371" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>135827249</v>
       </c>
       <c r="B374" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>136394245</v>
       </c>
       <c r="B376" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>136159865</v>
       </c>
       <c r="B384" t="n">
-        <v>96759</v>
+        <v>96772</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>136423160</v>
       </c>
       <c r="B386" t="n">
-        <v>92888</v>
+        <v>92901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>136423202</v>
       </c>
       <c r="B389" t="n">
-        <v>92921</v>
+        <v>92934</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         <v>135359246</v>
       </c>
       <c r="B464" t="n">
-        <v>91559</v>
+        <v>91572</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>136139193</v>
       </c>
       <c r="B475" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>136159751</v>
       </c>
       <c r="B476" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -54556,7 +54556,7 @@
         <v>136159959</v>
       </c>
       <c r="B477" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>136159979</v>
       </c>
       <c r="B478" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -54768,7 +54768,7 @@
         <v>136193282</v>
       </c>
       <c r="B479" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -54874,7 +54874,7 @@
         <v>136193424</v>
       </c>
       <c r="B480" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>136232449</v>
       </c>
       <c r="B481" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>136394238</v>
       </c>
       <c r="B482" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -55632,7 +55632,7 @@
         <v>136394243</v>
       </c>
       <c r="B487" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -56624,7 +56624,7 @@
         <v>136259823</v>
       </c>
       <c r="B496" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>136394239</v>
       </c>
       <c r="B497" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -57434,7 +57434,7 @@
         <v>136160087</v>
       </c>
       <c r="B503" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -58340,7 +58340,7 @@
         <v>136394241</v>
       </c>
       <c r="B511" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -58452,7 +58452,7 @@
         <v>136394242</v>
       </c>
       <c r="B512" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         <v>136138429</v>
       </c>
       <c r="B531" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -60615,7 +60615,7 @@
         <v>136422471</v>
       </c>
       <c r="B532" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>136422534</v>
       </c>
       <c r="B533" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>136422649</v>
       </c>
       <c r="B534" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -62152,7 +62152,7 @@
         <v>136138543</v>
       </c>
       <c r="B546" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -62262,7 +62262,7 @@
         <v>136138586</v>
       </c>
       <c r="B547" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -63356,7 +63356,7 @@
         <v>136234180</v>
       </c>
       <c r="B557" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -63458,7 +63458,7 @@
         <v>136394244</v>
       </c>
       <c r="B558" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -63570,7 +63570,7 @@
         <v>136234148</v>
       </c>
       <c r="B559" t="n">
-        <v>98193</v>
+        <v>98206</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -65435,7 +65435,7 @@
         <v>135827336</v>
       </c>
       <c r="B576" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -65541,7 +65541,7 @@
         <v>136422957</v>
       </c>
       <c r="B577" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -66973,7 +66973,7 @@
         <v>136423088</v>
       </c>
       <c r="B590" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -71726,7 +71726,7 @@
         <v>136268106</v>
       </c>
       <c r="B633" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -72735,7 +72735,7 @@
         <v>136138855</v>
       </c>
       <c r="B642" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -73092,7 +73092,7 @@
         <v>136241491</v>
       </c>
       <c r="B645" t="n">
-        <v>58830</v>
+        <v>58843</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -73542,7 +73542,7 @@
         <v>136394236</v>
       </c>
       <c r="B649" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -79196,7 +79196,7 @@
         <v>136422855</v>
       </c>
       <c r="B701" t="n">
-        <v>90824</v>
+        <v>90837</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -79522,7 +79522,7 @@
         <v>136422890</v>
       </c>
       <c r="B704" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -79857,7 +79857,7 @@
         <v>136159945</v>
       </c>
       <c r="B707" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -80198,7 +80198,7 @@
         <v>136226883</v>
       </c>
       <c r="B710" t="n">
-        <v>96663</v>
+        <v>96676</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -80632,7 +80632,7 @@
         <v>136193016</v>
       </c>
       <c r="B714" t="n">
-        <v>91574</v>
+        <v>91587</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -80960,7 +80960,7 @@
         <v>136159708</v>
       </c>
       <c r="B717" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -81070,7 +81070,7 @@
         <v>136239010</v>
       </c>
       <c r="B718" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -83158,7 +83158,7 @@
         <v>135358856</v>
       </c>
       <c r="B737" t="n">
-        <v>91559</v>
+        <v>91572</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -83268,7 +83268,7 @@
         <v>136241603</v>
       </c>
       <c r="B738" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -83385,7 +83385,7 @@
         <v>136231090</v>
       </c>
       <c r="B739" t="n">
-        <v>96631</v>
+        <v>96644</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -83487,7 +83487,7 @@
         <v>136138371</v>
       </c>
       <c r="B740" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -83593,7 +83593,7 @@
         <v>136259499</v>
       </c>
       <c r="B741" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -83823,7 +83823,7 @@
         <v>136394237</v>
       </c>
       <c r="B743" t="n">
-        <v>92499</v>
+        <v>92512</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -85463,7 +85463,7 @@
         <v>136241765</v>
       </c>
       <c r="B758" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -86258,7 +86258,7 @@
         <v>136138879</v>
       </c>
       <c r="B765" t="n">
-        <v>58006</v>
+        <v>58019</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -86711,7 +86711,7 @@
         <v>136138971</v>
       </c>
       <c r="B769" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -86821,7 +86821,7 @@
         <v>136193477</v>
       </c>
       <c r="B770" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
